--- a/Files/BusinessLogic_Functions.xlsx
+++ b/Files/BusinessLogic_Functions.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="57">
   <si>
     <t>Function</t>
   </si>
@@ -41,69 +41,81 @@
     <t>Execute(Y/N)</t>
   </si>
   <si>
+    <t>launch&amp;login</t>
+  </si>
+  <si>
+    <t>launchURL</t>
+  </si>
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>enterText</t>
+  </si>
+  <si>
+    <t>userName</t>
+  </si>
+  <si>
+    <t>password</t>
+  </si>
+  <si>
+    <t>click</t>
+  </si>
+  <si>
+    <t>ClickloginButton</t>
+  </si>
+  <si>
+    <t>validate</t>
+  </si>
+  <si>
+    <t>Dashboard</t>
+  </si>
+  <si>
+    <t>addEmployeeData</t>
+  </si>
+  <si>
+    <t>ClickPIM</t>
+  </si>
+  <si>
+    <t>ClickAddEmployee</t>
+  </si>
+  <si>
+    <t>empFirstName</t>
+  </si>
+  <si>
+    <t>empMiddleName</t>
+  </si>
+  <si>
+    <t>empLastName</t>
+  </si>
+  <si>
+    <t>empID</t>
+  </si>
+  <si>
+    <t>empSaveButton</t>
+  </si>
+  <si>
+    <t>validateUsingReplace</t>
+  </si>
+  <si>
+    <t>validateEmployeeCreation</t>
+  </si>
+  <si>
+    <t>logout</t>
+  </si>
+  <si>
+    <t>ClickUserIcon</t>
+  </si>
+  <si>
+    <t>ClickLogout</t>
+  </si>
+  <si>
     <t>login</t>
   </si>
   <si>
-    <t>launchURL</t>
-  </si>
-  <si>
-    <t>URL</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>enterText</t>
-  </si>
-  <si>
-    <t>userName</t>
-  </si>
-  <si>
-    <t>password</t>
-  </si>
-  <si>
-    <t>click</t>
-  </si>
-  <si>
-    <t>ClickloginButton</t>
-  </si>
-  <si>
-    <t>validate</t>
-  </si>
-  <si>
-    <t>Dashboard</t>
-  </si>
-  <si>
-    <t>addEmployeeData</t>
-  </si>
-  <si>
-    <t>ClickPIM</t>
-  </si>
-  <si>
-    <t>ClickAddEmployee</t>
-  </si>
-  <si>
-    <t>empFirstName</t>
-  </si>
-  <si>
-    <t>empMiddleName</t>
-  </si>
-  <si>
-    <t>empLastName</t>
-  </si>
-  <si>
-    <t>empID</t>
-  </si>
-  <si>
-    <t>empSaveButton</t>
-  </si>
-  <si>
-    <t>validateUsingReplace</t>
-  </si>
-  <si>
-    <t>validateEmployeeCreation</t>
-  </si>
-  <si>
     <t>addJobVacancy</t>
   </si>
   <si>
@@ -119,25 +131,34 @@
     <t>vacancyName</t>
   </si>
   <si>
-    <t>jobTitle</t>
+    <t>ClickJobTitleDropdown</t>
   </si>
   <si>
     <t>clickUsingReplace</t>
   </si>
   <si>
-    <t>ClickjobTitleOption</t>
+    <t>ClickJobTitleOption</t>
   </si>
   <si>
     <t>description</t>
   </si>
   <si>
+    <t>enterTextKeyboardAction</t>
+  </si>
+  <si>
     <t>hiringManager</t>
   </si>
   <si>
     <t>noOfPositions</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>saveVacancyButton</t>
+  </si>
+  <si>
+    <t>exist</t>
+  </si>
+  <si>
+    <t>validateVacancyCreation</t>
   </si>
   <si>
     <t>addCandidateData</t>
@@ -167,13 +188,16 @@
     <t>email</t>
   </si>
   <si>
-    <t>resume</t>
+    <t>contactNo</t>
   </si>
   <si>
     <t>notes</t>
   </si>
   <si>
     <t>ClickCandidateSaveButton</t>
+  </si>
+  <si>
+    <t>validateCandidateStatus</t>
   </si>
 </sst>
 </file>
@@ -1146,7 +1170,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="25.3611111111111" customWidth="1"/>
@@ -1379,13 +1403,13 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>7</v>
@@ -1393,13 +1417,13 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>29</v>
+      <c r="C18" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>7</v>
@@ -1407,13 +1431,13 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="4" t="s">
-        <v>30</v>
+      <c r="C19" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>7</v>
@@ -1421,13 +1445,13 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>30</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>7</v>
@@ -1435,13 +1459,13 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>33</v>
+        <v>11</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>31</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>7</v>
@@ -1449,13 +1473,13 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>34</v>
+        <v>11</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>7</v>
@@ -1463,13 +1487,13 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>7</v>
@@ -1477,13 +1501,13 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>36</v>
+      <c r="C24" s="4" t="s">
+        <v>34</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>7</v>
@@ -1491,13 +1515,13 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>36</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>7</v>
@@ -1505,13 +1529,13 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>7</v>
@@ -1519,12 +1543,12 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>39</v>
       </c>
       <c r="D27" s="2" t="s">
@@ -1533,27 +1557,27 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="4" t="s">
         <v>40</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>7</v>
@@ -1561,10 +1585,10 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>43</v>
@@ -1575,13 +1599,13 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>7</v>
@@ -1589,10 +1613,10 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>45</v>
@@ -1603,7 +1627,7 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>8</v>
@@ -1617,7 +1641,7 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>8</v>
@@ -1626,20 +1650,120 @@
         <v>47</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C35" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D35" s="2"/>
+      <c r="C36" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
